--- a/resources/templates/standard/K1200-04.xlsx
+++ b/resources/templates/standard/K1200-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>업체실태 조사서 (갑지)</t>
   </si>
@@ -744,12 +747,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -769,20 +774,20 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
@@ -857,7 +862,7 @@
     </row>
     <row r="4" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -875,7 +880,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -895,7 +900,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -913,7 +918,7 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5" s="10"/>
       <c r="S5" s="10"/>
@@ -933,11 +938,11 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="11"/>
       <c r="C6" s="10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -973,7 +978,7 @@
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1009,7 +1014,7 @@
       <c r="A8" s="11"/>
       <c r="B8" s="11"/>
       <c r="C8" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1043,7 +1048,7 @@
     </row>
     <row r="9" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -1059,7 +1064,7 @@
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P9" s="10"/>
       <c r="Q9" s="10"/>
@@ -1081,7 +1086,7 @@
     </row>
     <row r="10" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -1097,23 +1102,23 @@
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
       <c r="T10" s="10"/>
       <c r="U10" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V10" s="10"/>
       <c r="W10" s="10"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z10" s="10"/>
       <c r="AA10" s="10"/>
@@ -1125,14 +1130,14 @@
     </row>
     <row r="11" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
@@ -1168,7 +1173,7 @@
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
       <c r="F12" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -1199,14 +1204,14 @@
     </row>
     <row r="13" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="F13" s="16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
@@ -1242,7 +1247,7 @@
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
       <c r="F14" s="18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
@@ -1278,7 +1283,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
@@ -1314,7 +1319,7 @@
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
       <c r="F16" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
@@ -1345,14 +1350,14 @@
     </row>
     <row r="17" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
@@ -1456,7 +1461,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
@@ -1560,7 +1565,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
@@ -1659,7 +1664,7 @@
     </row>
     <row r="26" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -1763,7 +1768,7 @@
     </row>
     <row r="29" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -1781,19 +1786,19 @@
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
       <c r="T29" s="10"/>
       <c r="U29" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
       <c r="X29" s="5"/>
       <c r="Y29" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z29" s="12"/>
       <c r="AA29" s="12"/>
@@ -1825,13 +1830,13 @@
       <c r="S30" s="10"/>
       <c r="T30" s="10"/>
       <c r="U30" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="V30" s="5"/>
       <c r="W30" s="5"/>
       <c r="X30" s="5"/>
       <c r="Y30" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z30" s="12"/>
       <c r="AA30" s="12"/>
@@ -1863,13 +1868,13 @@
       <c r="S31" s="10"/>
       <c r="T31" s="10"/>
       <c r="U31" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
       <c r="X31" s="5"/>
       <c r="Y31" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Z31" s="12"/>
       <c r="AA31" s="12"/>
@@ -1881,14 +1886,14 @@
     </row>
     <row r="32" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G32" s="9"/>
       <c r="H32" s="9"/>
@@ -1903,7 +1908,7 @@
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="9"/>
@@ -1926,7 +1931,7 @@
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G33" s="9"/>
       <c r="H33" s="9"/>
@@ -1941,7 +1946,7 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
@@ -1964,7 +1969,7 @@
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G34" s="21"/>
       <c r="H34" s="21"/>
@@ -1979,7 +1984,7 @@
       <c r="Q34" s="21"/>
       <c r="R34" s="21"/>
       <c r="S34" s="21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="T34" s="21"/>
       <c r="U34" s="21"/>
@@ -2001,7 +2006,7 @@
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
@@ -2101,7 +2106,7 @@
     </row>
     <row r="38" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -2137,11 +2142,11 @@
     </row>
     <row r="39" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="23"/>
       <c r="C39" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2152,7 +2157,7 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
@@ -2163,12 +2168,12 @@
       <c r="S39" s="5"/>
       <c r="T39" s="5"/>
       <c r="U39" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
       <c r="X39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
@@ -2176,7 +2181,7 @@
       <c r="AB39" s="5"/>
       <c r="AC39" s="5"/>
       <c r="AD39" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AE39" s="5"/>
       <c r="AF39" s="5"/>
@@ -2659,7 +2664,7 @@
     </row>
     <row r="54" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -2695,11 +2700,11 @@
     </row>
     <row r="55" ht="20.1" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B55" s="23"/>
       <c r="C55" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
@@ -2710,7 +2715,7 @@
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
@@ -2721,12 +2726,12 @@
       <c r="S55" s="5"/>
       <c r="T55" s="5"/>
       <c r="U55" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="V55" s="5"/>
       <c r="W55" s="5"/>
       <c r="X55" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
@@ -2734,7 +2739,7 @@
       <c r="AB55" s="5"/>
       <c r="AC55" s="5"/>
       <c r="AD55" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AE55" s="5"/>
       <c r="AF55" s="5"/>
